--- a/data_extactor/batch_10_fa/batch_0091_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0091_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>نرم‌افزار ثبت داده‌ها | نرم‌افزار پایگاه داده | سیستم‌های اطلاعات جغرافیایی GIS | نرم‌افزار رابط انسان و ماشین HMI | نرم‌افزار برگه اطلاعات ایمنی مواد MSDS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار ذخیره‌سازی داده‌های عملیاتی ODS | نرم‌افزار مدیریت سوابق | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار ثبت زمان حضور و غیاب | سیستم‌های کنترل هوشمند تصفیه فاضلاب</t>
+          <t>نرم‌افزار ثبت داده‌ها | نرم‌افزار پایگاه داده | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار رابط انسان و ماشین HMI | نرم‌افزار برگه اطلاعات ایمنی مواد MSDS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار ذخیره‌سازی داده‌های عملیاتی ODS | نرم‌افزار مدیریت سوابق | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار ثبت زمان | سیستم‌های کنترل هوشمند تصفیه فاضلاب</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب خوانده‌شده</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>امنیت و ایمنی عمومی | مکانیک | زبان انگلیسی | شیمی | ریاضیات | امور اداری و مدیریت | آموزش و پرورش | خدمات مشتریان و پرسنل | کامپیوتر و الکترونیک | قوانین و مقررات دولتی | مهندسی و فناوری | زیست‌شناسی | اداری | تولید و فرآوری</t>
+          <t>ایمنی و امنیت عمومی | مکانیک | زبان انگلیسی | شیمی | ریاضیات | مدیریت و اداره | آموزش و پرورش | خدمات مشتری و شخصی | رایانه و الکترونیک | قانون و دولت | مهندسی و فناوری | زیست‌شناسی | اداری | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | استدلال قیاسی | درک کتبی | دقت کنترل | توجه انتخابی | ترتیب‌دهی به اطلاعات | استدلال استقرایی | حساسیت به مسائل | بیان کتبی | قدرت بدنی بالاتنه | چالاکی دست | ثبات دست و بازو | سرعت ادراکی | انعطاف‌پذیری در بستن فضا | وضوح گفتار | تشخیص گفتار | بینایی دور</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | استدلال قیاسی | درک کتبی | دقت کنترل | توجه انتخابی | ترتیب‌دهی اطلاعات | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | قدرت تنه | مهارت دستی | ثبات دست و بازو | سرعت ادراکی | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص گفتار | بینایی دور</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | در خودروی سرپوشیده یا کار با تجهیزات سرپوشیده | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای بسته، بدون کنترل شرایط محیطی | در معرض آلاینده‌ها | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فضای بسته، با کنترل شرایط محیطی | در معرض شرایط خطرناک | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه یا تیم کاری | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا درست بودن کار | ارتباط با دیگران | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | فضای باز، زیر سایه‌بان | در معرض تجهیزات خطرناک | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان | پیامد اشتباه | نزدیکی فیزیکی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | در معرض دماهای بسیار گرم یا سرد | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | محیط داخلی، دارای کنترل شرایط محیطی | قرار گرفتن در معرض شرایط خطرناک | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا درست بودن | ارتباط با دیگران | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | فضای باز، زیر سقف | قرار گرفتن در معرض تجهیزات خطرناک | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان | پیامد خطا | نزدیکی فیزیکی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنسین‌های فرآوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورهای سیستم و کارخانجات شیمیایی | اپراتورها و متصدیان تجهیزات شستشو، پاکسازی و اسیدشویی فلزات | تکنسین‌های علوم و حفاظت محیط زیست، از جمله بهداشت | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای پالایشگاه گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | کارگران حذف مواد خطرناک | تکنسین‌های نیروگاه برق‌آبی | اپراتورهای سیستم پمپ نفت، اپراتورهای پالایشگاه و سنجش‌گران | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به جز پمپ‌های سرچاهی | کارگران بازیافت و احیای مواد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، رسوب‌دهی و تقطیر | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | مهندسان تاسیسات و اپراتورهای دیگ بخار | مهندسان آب و فاضلاب</t>
+          <t>تکنسین‌های فرآوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | متصدیان و اپراتورهای تجهیزات شیمیایی | اپراتورهای کارخانه و سامانه‌های شیمیایی | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای واحدهای گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | کارگران حذف مواد خطرناک | تکنسین‌های نیروگاه برق‌آبی | اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | کارگران بازیافت و احیا | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | مهندسان تاسیسات و اپراتورهای دیگ بخار | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chemical Plant and System Operators</t>
+          <t>اپراتورهای کارخانه و سامانه‌های شیمیایی (Chemical Plant and System Operators)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>مانیتورینگ | تفکر انتقادی | گوش دادن فعال | یادگیری فعال | درک مطلب خوانده‌شده | سخن گفتن | نگارش</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | یادگیری فعال | درک مطلب | سخن گفتن | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | شیمی | مکانیک | زبان انگلیسی | امنیت و ایمنی عمومی | خدمات مشتریان و پرسنل</t>
+          <t>تولید و فرآوری | شیمی | مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مسائل | توجه انتخابی | بینایی نزدیک | بیان شفاهی | استدلال قیاسی | درک شفاهی | بینایی دور | دقت کنترل | سرعت ادراکی | ترتیب‌دهی به اطلاعات | حساسیت شنوایی | ثبات دست و بازو | درک کتبی | زمان عکس‌العمل | توجه شنوایی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ‌های بصری | چالاکی دست | انعطاف‌پذیری در بستن فضا | استدلال استقرایی | بیان کتبی | چالاکی انگشتان | انعطاف‌پذیری دسته‌بندی</t>
+          <t>حساسیت به مسئله | توجه انتخابی | بینایی نزدیک | بیان شفاهی | استدلال قیاسی | درک شفاهی | بینایی دور | دقت کنترل | سرعت ادراکی | ترتیب‌دهی اطلاعات | حساسیت شنوایی | ثبات دست و بازو | درک کتبی | زمان عکس‌العمل | توجه شنیداری | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | مهارت دستی | انعطاف‌پذیری بستار | استدلال استقرایی | بیان کتبی | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | در معرض شرایط خطرناک | در معرض آلاینده‌ها | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فضای بسته، بدون کنترل شرایط محیطی | فراوانی تصمیم‌گیری | مکالمات تلفنی | فضای بسته، با کنترل شرایط محیطی | فضای باز، در معرض تمام شرایط آب و هوایی | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا درست بودن کار | سرعت کار تعیین‌شده توسط تجهیزات | ارتباط با دیگران | آزادی در تصمیم‌گیری | فضای باز، زیر سایه‌بان | پیامد اشتباه | فشار زمانی | کار با یا مشارکت در یک گروه یا تیم کاری | در معرض دماهای بسیار گرم یا سرد | اهمیت تکرار وظایف یکسان | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | در معرض ارتفاعات بالا | در معرض تجهیزات خطرناک | میزان اتوماسیون | پیامدهای کاری و نتایج سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | ایمیل</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | محیط داخلی، بدون کنترل شرایط محیطی | فراوانی تصمیم‌گیری | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | فضای باز، در معرض تمام شرایط آب و هوایی | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا درست بودن | سرعت تعیین‌شده توسط سرعت تجهیزات | ارتباط با دیگران | آزادی در تصمیم‌گیری | فضای باز، زیر سقف | پیامد خطا | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | اهمیت تکرار وظایف یکسان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض ارتفاعات بالا | قرار گرفتن در معرض تجهیزات خطرناک | میزان خودکارسازی | پیامدهای کاری و نتایج سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | ایمیل</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تکنسین‌های فرآوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مهندسان شیمی | اپراتورها و متصدیان تجهیزات شیمیایی | تکنسین‌های شیمی | شیمی‌دان‌ها | اپراتورها و متصدیان تجهیزات شستشو، پاکسازی و اسیدشویی فلزات | اپراتورها و متصدیان کوره، تنور، خشک‌کن و دیگ‌های ذوب | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای پالایشگاه گاز | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | اپراتورها و متصدیان کوره‌های تصفیه فلز | اپراتورهای سیستم پمپ نفت، اپراتورهای پالایشگاه و سنجش‌گران | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به جز پمپ‌های سرچاهی | تکنسین‌های فرآوری نیمه‌هادی‌ها | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، رسوب‌دهی و تقطیر | مهندسان تاسیسات و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
+          <t>تکنسین‌های فرآوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مهندسان شیمی | متصدیان و اپراتورهای تجهیزات شیمیایی | تکنسین‌های شیمی | شیمی‌دانان | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای واحدهای گاز | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | اپراتورها و متصدیان کوره تصفیه فلز | اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | تکنسین‌های فرآوری نیمه‌رساناها | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | مهندسان تاسیسات و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gas Plant Operators</t>
+          <t>اپراتورهای واحدهای گاز (Gas Plant Operators)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AspenTech HYSYS | Google Android | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار ثبت وقایع عملیاتی | Quorum PGAS | نرم‌افزار SAP | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار برنامه‌ریزی کاری</t>
+          <t>AspenTech HYSYS | Google Android | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار ثبت وقایع عملیاتی | Quorum PGAS | نرم‌افزار SAP | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار زمان‌بندی کار</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>مانیتورینگ | تفکر انتقادی | درک مطلب خوانده‌شده | سخن گفتن | نگارش | گوش دادن فعال</t>
+          <t>نظارت | تفکر انتقادی | درک مطلب | سخن گفتن | نگارش | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>امنیت و ایمنی عمومی | مکانیک | زبان انگلیسی | کامپیوتر و الکترونیک | ریاضیات | مهندسی و فناوری | تولید و فرآوری | خدمات مشتریان و پرسنل | اداری</t>
+          <t>ایمنی و امنیت عمومی | مکانیک | زبان انگلیسی | رایانه و الکترونیک | ریاضیات | مهندسی و فناوری | تولید و فرآوری | خدمات مشتری و شخصی | اداری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>سرعت ادراکی | بینایی نزدیک | حساسیت به مسائل | توجه شنوایی | توجه انتخابی | درک شفاهی | استدلال قیاسی | انعطاف‌پذیری در بستن فضا | بینایی دور | زمان عکس‌العمل | ترتیب‌دهی به اطلاعات | بیان کتبی | درک کتبی | تقسیم توجه | تجسم فضایی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت شنوایی | تشخیص رنگ‌های بصری | کنترل نرخ سرعت | دقت کنترل | چالاکی انگشتان | چالاکی دست | ثبات دست و بازو</t>
+          <t>سرعت ادراکی | بینایی نزدیک | حساسیت به مسئله | توجه شنیداری | توجه انتخابی | درک شفاهی | استدلال قیاسی | انعطاف‌پذیری بستار | بینایی دور | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | بیان کتبی | درک کتبی | تقسیم توجه | تجسم | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت شنوایی | تشخیص رنگ بصری | کنترل نرخ | دقت کنترل | مهارت انگشتان | مهارت دستی | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | ایمیل | اهمیت دقیق یا درست بودن کار | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه یا تیم کاری | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فضای باز، در معرض تمام شرایط آب و هوایی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پیامد اشتباه | سلامت و ایمنی سایر کارکنان | آزادی در تصمیم‌گیری | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | در معرض شرایط خطرناک | در معرض آلاینده‌ها | اهمیت تکرار وظایف یکسان | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فضای بسته، با کنترل شرایط محیطی | در خودروی سرپوشیده یا کار با تجهیزات سرپوشیده | در معرض دماهای بسیار گرم یا سرد | فشار زمانی</t>
+          <t>مکالمات تلفنی | ایمیل | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فضای باز، در معرض تمام شرایط آب و هوایی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامد خطا | سلامت و ایمنی سایر کارکنان | آزادی در تصمیم‌گیری | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض آلاینده‌ها | اهمیت تکرار وظایف یکسان | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | محیط داخلی، دارای کنترل شرایط محیطی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فشار زمانی</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تکنسین‌های فرآوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه برق زیست‌توده | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورهای سیستم و کارخانجات شیمیایی | نصابان و تعمیرکنندگان شیرآلات و کنترل‌ها، به جز درب‌های مکانیکی | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | اپراتورهای سیستم پمپ نفت، اپراتورهای پالایشگاه و سنجش‌گران | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به جز پمپ‌های سرچاهی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، رسوب‌دهی و تقطیر | اپراتورهای واحدهای خدمات چاه نفت و گاز | مهندسان تاسیسات و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | پمپ‌کنندگان سرچاهی | تکنسین‌های خدمات توربین بادی</t>
+          <t>تکنسین‌های فرآوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | متصدیان و اپراتورهای تجهیزات شیمیایی | اپراتورهای کارخانه و سامانه‌های شیمیایی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | اپراتورهای واحد خدمات، نفت و گاز | مهندسان تاسیسات و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | پمپ‌کنندگان سرچاهی | تکنسین‌های خدمات توربین بادی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Petroleum Pump System Operators, Refinery Operators, and Gaugers</t>
+          <t>اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری (Petroleum Pump System Operators, Refinery Operators, and Gaugers)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>مانیتورینگ | درک مطلب خوانده‌شده | سخن گفتن | یادگیری فعال | تفکر انتقادی | نگارش | گوش دادن فعال</t>
+          <t>نظارت | درک مطلب | سخن گفتن | یادگیری فعال | تفکر انتقادی | نگارش | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | امنیت و ایمنی عمومی | مکانیک | امور اداری و مدیریت | ریاضیات | زبان انگلیسی</t>
+          <t>تولید و فرآوری | ایمنی و امنیت عمومی | مکانیک | مدیریت و اداره | ریاضیات | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ترتیب‌دهی به اطلاعات | انعطاف‌پذیری در بستن فضا | سرعت ادراکی | بینایی نزدیک | حساسیت به مسائل | توجه انتخابی | توجه شنوایی | حساسیت شنوایی | استدلال قیاسی | تشخیص گفتار | دقت کنترل | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | درک کتبی | درک شفاهی | چالاکی انگشتان | چالاکی دست | ثبات دست و بازو | تجسم فضایی | بیان کتبی | تشخیص رنگ‌های بصری | بینایی دور | زمان عکس‌العمل | هماهنگی چند عضو بدن | وضوح گفتار</t>
+          <t>ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | سرعت ادراکی | بینایی نزدیک | حساسیت به مسئله | توجه انتخابی | توجه شنیداری | حساسیت شنوایی | استدلال قیاسی | تشخیص گفتار | دقت کنترل | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | درک کتبی | درک شفاهی | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | تجسم | بیان کتبی | تشخیص رنگ بصری | بینایی دور | زمان عکس‌العمل | هماهنگی چند عضو | وضوح گفتار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | در معرض شرایط خطرناک | در معرض آلاینده‌ها | در معرض دماهای بسیار گرم یا سرد | کار با یا مشارکت در یک گروه یا تیم کاری | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | مکالمات تلفنی | در معرض ارتفاعات بالا | ارتباط با دیگران | پیامد اشتباه | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن کار | سلامت و ایمنی سایر کارکنان | ایمیل | فضای باز، زیر سایه‌بان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فضای بسته، با کنترل شرایط محیطی | در معرض شرایط نوری بسیار روشن یا ناکافی | اهمیت تکرار وظایف یکسان | فشار زمانی | آزادی در تصمیم‌گیری | در معرض تجهیزات خطرناک | نامه‌ها و یادداشت‌های کتبی | پیامدهای کاری و نتایج سایر کارکنان | فضای بسته، بدون کنترل شرایط محیطی | در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | مکالمات تلفنی | قرار گرفتن در معرض ارتفاعات بالا | ارتباط با دیگران | پیامد خطا | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | ایمیل | فضای باز، زیر سقف | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | محیط داخلی، دارای کنترل شرایط محیطی | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | اهمیت تکرار وظایف یکسان | فشار زمانی | آزادی در تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک | نامه‌ها و یادداشت‌های کتبی | پیامدهای کاری و نتایج سایر کارکنان | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنسین‌های فرآوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه برق زیست‌توده | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورهای سیستم و کارخانجات شیمیایی | نصابان و تعمیرکنندگان شیرآلات و کنترل‌ها، به جز درب‌های مکانیکی | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای پالایشگاه گاز | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مهندسان نفت | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به جز پمپ‌های سرچاهی | اپراتورهای دکل حفاری دورانی، نفت و گاز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، رسوب‌دهی و تقطیر | اپراتورهای واحدهای خدمات چاه نفت و گاز | مهندسان تاسیسات و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | پمپ‌کنندگان سرچاهی</t>
+          <t>تکنسین‌های فرآوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | متصدیان و اپراتورهای تجهیزات شیمیایی | اپراتورهای کارخانه و سامانه‌های شیمیایی | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای واحدهای گاز | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مهندسان نفت | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | اپراتورهای مته چرخشی، نفت و گاز | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | اپراتورهای واحد خدمات، نفت و گاز | مهندسان تاسیسات و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | پمپ‌کنندگان سرچاهی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Plant and System Operators, All Other</t>
+          <t>اپراتورهای کارخانه و سامانه‌ها، سایر موارد (Plant and System Operators, All Other)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | نرم‌افزار کنترل فرآیند آماری SPC | نرم‌افزار برنامه‌ریزی مواد مورد نیاز MRP | سیستم مدیریت کامپیوتری تعمیر و نگهداری CMMS | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | سیستم‌های مدیریت موجودی | سیستم برنامه‌ریزی منابع سازمانی ERP | نرم‌افزار پایگاه داده | نرم‌افزار SAP</t>
+          <t>نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | نرم‌افزار کنترل فرآیند آماری SPC | نرم‌افزار برنامه‌ریزی نیازمندی‌های مواد MRP | سیستم مدیریت نگهداری کامپیوتری CMMS | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | سیستم‌های مدیریت موجودی | سیستم برنامه‌ریزی منابع سازمانی ERP | نرم‌افزار پایگاه داده | نرم‌افزار SAP</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب خوانده‌شده | تفکر انتقادی | مانیتورینگ | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مکانیک | تولید و فرآوری | فیزیک | شیمی | کامپیوتر و الکترونیک | زبان انگلیسی | ریاضیات | امنیت و ایمنی عمومی | مهندسی و فناوری</t>
+          <t>مکانیک | تولید و فرآوری | فیزیک | شیمی | رایانه و الکترونیک | زبان انگلیسی | ریاضیات | ایمنی و امنیت عمومی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسائل | ترتیب‌دهی به اطلاعات | بینایی نزدیک | تجسم فضایی | ثبات دست و بازو | چالاکی انگشتان | چالاکی دست | دقت کنترل | هماهنگی چند عضو بدن | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی دور | توجه شنوایی | زمان عکس‌العمل</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی دور | توجه شنیداری | زمان عکس‌العمل</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>فضای بسته، بدون کنترل شرایط محیطی | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | در معرض آلاینده‌ها | در معرض تجهیزات خطرناک | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم شدن یا چرخاندن بدن | نزدیکی فیزیکی | سرعت کار تعیین‌شده توسط تجهیزات | سلامت و ایمنی سایر کارکنان | پیامد اشتباه | میزان اتوماسیون | اهمیت تکرار وظایف یکسان | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | کار با یا مشارکت در یک گروه یا تیم کاری | اهمیت دقیق یا درست بودن کار | در معرض شرایط خطرناک | فراوانی تصمیم‌گیری</t>
+          <t>محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم کردن یا چرخاندن بدن | نزدیکی فیزیکی | سرعت تعیین‌شده توسط سرعت تجهیزات | سلامت و ایمنی سایر کارکنان | پیامد خطا | میزان خودکارسازی | اهمیت تکرار وظایف یکسان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض شرایط خطرناک | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>اپراتورهای نیروگاه برق | مهندسان تاسیسات و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | اپراتورهای سیستم و کارخانجات شیمیایی | اپراتورهای پالایشگاه گاز | اپراتورهای سیستم پمپ نفت، اپراتورهای پالایشگاه و سنجش‌گران | اپراتورهای راکتور هسته‌ای | توزیع‌کنندگان و دیسپچرهای برق | تکنسین‌های نیروگاه زیست‌توده | تکنسین‌های نیروگاه برق‌آبی | تکنسین‌های فرآوری سوخت‌های زیستی | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای پمپ، به جز پمپ‌های سرچاهی | مکانیک‌های ماشین‌آلات صنعتی | کارگران عمومی نگهداری و تعمیرات | سرپرستان خط اول کارگران تولید و عملیاتی | نصابان و تعمیرکنندگان شیرآلات و کنترل‌ها، به جز درب‌های مکانیکی | تکنسین‌های بهداشت و ایمنی حرفه‌ای | کارگران تولید، سایر</t>
+          <t>اپراتورهای نیروگاه برق | مهندسان تاسیسات و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | اپراتورهای کارخانه و سامانه‌های شیمیایی | اپراتورهای واحدهای گاز | اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری | اپراتورهای راکتور قدرت هسته‌ای | توزیع‌کنندگان و دیسپچرهای برق | تکنسین‌های نیروگاه زیست‌توده | تکنسین‌های نیروگاه برق‌آبی | تکنسین‌های فرآوری سوخت‌های زیستی | متصدیان و اپراتورهای تجهیزات شیمیایی | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | مکانیک‌های ماشین‌آلات صنعتی | کارگران نگهداری و تعمیرات عمومی | سرپرستان رده اول کارگران تولید و بهره‌برداری | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تکنسین‌های بهداشت و ایمنی شغلی | کارگران تولید، سایر موارد</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Biofuels Processing Technicians</t>
+          <t>تکنسین‌های فرآوری سوخت‌های زیستی (Biofuels Processing Technicians)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>سیستم مدیریت کامپیوتری تعمیر و نگهداری CMMS | نرم‌افزار تصویرسازی داده‌ها | سیستم‌های کنترل دیجیتال DCS | نرم‌افزار رابط انسان و ماشین HMI | نرم‌افزار کنترل موجودی | Microsoft Excel | Microsoft Word | Python | R | SAS | Tableau</t>
+          <t>سیستم مدیریت نگهداری کامپیوتری CMMS | نرم‌افزار تجسم داده | سیستم‌های کنترل دیجیتال DCS | نرم‌افزار رابط انسان و ماشین HMI | نرم‌افزار کنترل موجودی | Microsoft Excel | Microsoft Word | Python | R | SAS | Tableau</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب خوانده‌شده | مانیتورینگ | سخن گفتن | گوش دادن فعال | نگارش | تفکر انتقادی</t>
+          <t>درک مطلب | نظارت | سخن گفتن | گوش دادن فعال | نگارش | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | زبان انگلیسی | امنیت و ایمنی عمومی | شیمی | کامپیوتر و الکترونیک</t>
+          <t>تولید و فرآوری | مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | شیمی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دقت کنترل | تشخیص گفتار | درک شفاهی | بیان شفاهی | درک کتبی | ثبات دست و بازو | توجه انتخابی | سرعت ادراکی | ترتیب‌دهی به اطلاعات | استدلال استقرایی | استدلال قیاسی | حساسیت به مسائل | زمان عکس‌العمل | چالاکی دست | وضوح گفتار | تشخیص رنگ‌های بصری | بینایی نزدیک | چالاکی انگشتان | هماهنگی چند عضو بدن | بیان کتبی | توجه شنوایی | کنترل نرخ سرعت | تقسیم توجه | انعطاف‌پذیری در بستن فضا | انعطاف‌پذیری دسته‌بندی | تجسم فضایی | بینایی دور | انعطاف‌پذیری حرکتی | قدرت بدنی بالاتنه | حساسیت شنوایی</t>
+          <t>دقت کنترل | تشخیص گفتار | درک شفاهی | بیان شفاهی | درک کتبی | ثبات دست و بازو | توجه انتخابی | سرعت ادراکی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | زمان عکس‌العمل | مهارت دستی | وضوح گفتار | تشخیص رنگ بصری | بینایی نزدیک | مهارت انگشتان | هماهنگی چند عضو | بیان کتبی | توجه شنیداری | کنترل نرخ | تقسیم توجه | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | تجسم | بینایی دور | انعطاف‌پذیری دامنه حرکت | قدرت تنه | حساسیت شنوایی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | در معرض آلاینده‌ها | در معرض شرایط خطرناک | ارتباط با دیگران | فضای بسته، با کنترل شرایط محیطی | کار با یا مشارکت در یک گروه یا تیم کاری | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | در معرض دماهای بسیار گرم یا سرد | اهمیت دقیق یا درست بودن کار | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | سرعت کار تعیین‌شده توسط تجهیزات | فضای باز، در معرض تمام شرایط آب و هوایی | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | فضای بسته، بدون کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | در معرض ارتفاعات بالا | پیامد اشتباه | فشار زمانی | اهمیت تکرار وظایف یکسان | مکالمات تلفنی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | در خودروی بدون کابین یا کار با تجهیزات روباز | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فضای باز، زیر سایه‌بان | میزان اتوماسیون</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض شرایط خطرناک | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | سرعت تعیین‌شده توسط سرعت تجهیزات | فضای باز، در معرض تمام شرایط آب و هوایی | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | محیط داخلی، بدون کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض ارتفاعات بالا | پیامد خطا | فشار زمانی | اهمیت تکرار وظایف یکسان | مکالمات تلفنی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | در یک وسیله نقلیه روباز یا کار با تجهیزات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فضای باز، زیر سقف | میزان خودکارسازی</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنسین‌های کشاورزی | مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری سوخت زیستی/بیودیزل | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه برق زیست‌توده | مهندسان شیمی | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورهای سیستم و کارخانجات شیمیایی | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای پالایشگاه گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | تکنسین‌ها و تکنولوژیست‌های مهندسی صنایع | اپراتورهای سیستم پمپ نفت، اپراتورهای پالایشگاه و سنجش‌گران | اپراتورهای نیروگاه برق | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، رسوب‌دهی و تقطیر | مهندسان تاسیسات و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | پمپ‌کنندگان سرچاهی</t>
+          <t>تکنسین‌های کشاورزی | مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مهندسان شیمی | متصدیان و اپراتورهای تجهیزات شیمیایی | اپراتورهای کارخانه و سامانه‌های شیمیایی | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای واحدهای گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | تکنسین‌ها و کارشناسان مهندسی صنایع | اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری | اپراتورهای نیروگاه برق | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | مهندسان تاسیسات و اپراتورهای دیگ بخار | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | پمپ‌کنندگان سرچاهی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chemical Equipment Operators and Tenders</t>
+          <t>متصدیان و اپراتورهای تجهیزات شیمیایی (Chemical Equipment Operators and Tenders)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>مانیتورینگ | درک مطلب خوانده‌شده | گوش دادن فعال | تفکر انتقادی | سخن گفتن | یادگیری فعال | نگارش</t>
+          <t>نظارت | درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | شیمی | مکانیک | کامپیوتر و الکترونیک | زبان انگلیسی | ریاضیات | امنیت و ایمنی عمومی | قوانین و مقررات دولتی | اداری | امور اداری و مدیریت | مهندسی و فناوری | آموزش و پرورش</t>
+          <t>تولید و فرآوری | شیمی | مکانیک | رایانه و الکترونیک | زبان انگلیسی | ریاضیات | ایمنی و امنیت عمومی | قانون و دولت | اداری | مدیریت و اداره | مهندسی و فناوری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسائل | دقت کنترل | بینایی نزدیک | درک کتبی | سرعت ادراکی | بینایی دور | هماهنگی چند عضو بدن | ترتیب‌دهی به اطلاعات | چالاکی دست | زمان عکس‌العمل | بیان کتبی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | کنترل نرخ سرعت | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری در بستن فضا | استدلال استقرایی | توجه شنوایی | تشخیص رنگ‌های بصری | چالاکی انگشتان | تجسم فضایی | انعطاف‌پذیری دسته‌بندی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | دقت کنترل | بینایی نزدیک | درک کتبی | سرعت ادراکی | بینایی دور | هماهنگی چند عضو | ترتیب‌دهی اطلاعات | مهارت دستی | زمان عکس‌العمل | بیان کتبی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | کنترل نرخ | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری بستار | استدلال استقرایی | توجه شنیداری | تشخیص رنگ بصری | مهارت انگشتان | تجسم | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | در معرض آلاینده‌ها | در معرض شرایط خطرناک | سلامت و ایمنی سایر کارکنان | ایمیل | کار با یا مشارکت در یک گروه یا تیم کاری | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن کار | در معرض دماهای بسیار گرم یا سرد | فضای بسته، بدون کنترل شرایط محیطی | سرعت کار تعیین‌شده توسط تجهیزات | ارتباط با دیگران | فضای باز، در معرض تمام شرایط آب و هوایی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | پیامد اشتباه | آزادی در تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | اهمیت تکرار وظایف یکسان | در معرض تجهیزات خطرناک | تعیین وظایف، اولویت‌ها و اهداف | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | مکالمات تلفنی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان به صورت ایستاده | فراوانی تصمیم‌گیری | صرف زمان به صورت پیاده‌روی یا دویدن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض شرایط خطرناک | سلامت و ایمنی سایر کارکنان | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | محیط داخلی، بدون کنترل شرایط محیطی | سرعت تعیین‌شده توسط سرعت تجهیزات | ارتباط با دیگران | فضای باز، در معرض تمام شرایط آب و هوایی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | پیامد خطا | آزادی در تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض تجهیزات خطرناک | تعیین وظایف، اولویت‌ها و اهداف | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | مکالمات تلفنی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنسین‌های فرآوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مهندسان شیمی | اپراتورهای سیستم و کارخانجات شیمیایی | تکنسین‌های شیمی | اپراتورها و متصدیان تجهیزات شستشو، پاکسازی و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردکن، سنگ‌شکن و پولیش | اپراتورها و متصدیان کوره، تنور، خشک‌کن و دیگ‌های ذوب | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای پالایشگاه گاز | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلز و پلاستیک | اپراتورها و متصدیان کوره‌های تصفیه فلز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات مخلوط‌کن و همزن | اپراتورهای سیستم پمپ نفت، اپراتورهای پالایشگاه و سنجش‌گران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات آبکاری فلز و پلاست | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به جز پمپ‌های سرچاهی | تکنسین‌های فرآوری نیمه‌هادی‌ها | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، رسوب‌دهی و تقطیر | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
+          <t>تکنسین‌های فرآوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مهندسان شیمی | اپراتورهای کارخانه و سامانه‌های شیمیایی | تکنسین‌های شیمی | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | اپراتورهای واحدهای گاز | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | اپراتورها و متصدیان کوره تصفیه فلز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کننده | اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آبکاری، فلز و پلاستیک | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | تکنسین‌های فرآوری نیمه‌رساناها | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders</t>
+          <t>تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر (Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | مانیتورینگ | گوش دادن فعال | درک مطلب خوانده‌شده</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | سرعت ادراکی | حساسیت به مسائل | ثبات دست و بازو | ترتیب‌دهی به اطلاعات | زمان عکس‌العمل | قدرت بدنی ایستا | هماهنگی چند عضو بدن | دقت کنترل | توجه انتخابی | انعطاف‌پذیری در بستن فضا | درک شفاهی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | تشخیص گفتار | حساسیت شنوایی | تشخیص رنگ‌های بصری | بینایی دور | تعادل عمومی بدن | انعطاف‌پذیری حرکتی | قدرت بدنی بالاتنه | کنترل نرخ سرعت | چالاکی انگشتان | چالاکی دست | تجسم فضایی</t>
+          <t>بینایی نزدیک | سرعت ادراکی | حساسیت به مسئله | ثبات دست و بازو | ترتیب‌دهی اطلاعات | زمان عکس‌العمل | قدرت ایستا | هماهنگی چند عضو | دقت کنترل | توجه انتخابی | انعطاف‌پذیری بستار | درک شفاهی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | تشخیص گفتار | حساسیت شنوایی | تشخیص رنگ بصری | بینایی دور | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | قدرت تنه | کنترل نرخ | مهارت انگشتان | مهارت دستی | تجسم</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | در معرض آلاینده‌ها | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | آزادی در تصمیم‌گیری | فضای بسته، بدون کنترل شرایط محیطی | پیامد اشتباه | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | در معرض دماهای بسیار گرم یا سرد | کار با یا مشارکت در یک گروه یا تیم کاری | اهمیت دقیق یا درست بودن کار | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | موقعیت‌های تعارض‌آمیز | در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌زدگی‌ها | در معرض تجهیزات خطرناک | میزان اتوماسیون</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | آزادی در تصمیم‌گیری | محیط داخلی، بدون کنترل شرایط محیطی | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | موقعیت‌های تعارض | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض تجهیزات خطرناک | میزان خودکارسازی</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌های نیروگاه زیست‌توده | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورهای سیستم و کارخانجات شیمیایی | اپراتورها و متصدیان تجهیزات شستشو، پاکسازی و اسیدشویی فلزات | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردکن، سنگ‌شکن و پولیش | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات اکسترود و فرم‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات اکسترود، فرم‌دهی، پرس و متراکم‌سازی | بچ‌سازان مواد غذایی | اپراتورها و متصدیان ماشین‌آلات پخت مواد غذایی | اپراتورها و متصدیان ماشین‌آلات برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | اپراتورها و متصدیان کوره، تنور، خشک‌کن و دیگ‌های ذوب | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان کوره‌های تصفیه فلز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات مخلوط‌کن و همزن | اپراتورها و متصدیان ماشین‌آلات بسته‌بندی و پرکنی | اپراتورهای پمپ، به جز پمپ‌های سرچاهی | اپراتورها و متصدیان ماشین‌آلات رنگرزی و سفیدگری منسوجات | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
+          <t>تکنسین‌های نیروگاه زیست‌توده | متصدیان و اپراتورهای تجهیزات شیمیایی | اپراتورهای کارخانه و سامانه‌های شیمیایی | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | بچ‌سازان مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان کوره تصفیه فلز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کننده | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders</t>
+          <t>تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت (Crushing, Grinding, and Polishing Machine Setters, Operators, and Tenders)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>مانیتورینگ | سخن گفتن | گوش دادن فعال | درک مطلب خوانده‌شده</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>امور اداری و مدیریت | تولید و فرآوری | زبان انگلیسی | آموزش و پرورش | امنیت و ایمنی عمومی</t>
+          <t>مدیریت و اداره | تولید و فرآوری | زبان انگلیسی | آموزش و پرورش | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دستگاه‌های دستی | دقت کنترل | زمان عکس‌العمل | کنترل نرخ سرعت | هماهنگی چند عضو بدن | ثبات دست و بازو | بینایی نزدیک | حساسیت به مسائل | توجه شنوایی | قدرت بدنی بالاتنه | قدرت بدنی ایستا | چالاکی انگشتان | سرعت ادراکی | انعطاف‌پذیری در بستن فضا | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی | حساسیت شنوایی | تشخیص رنگ‌های بصری | انعطاف‌پذیری حرکتی | جهت‌یابی پاسخ | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار</t>
+          <t>مهارت دستی | دقت کنترل | زمان عکس‌العمل | کنترل نرخ | هماهنگی چند عضو | ثبات دست و بازو | بینایی نزدیک | حساسیت به مسئله | توجه شنیداری | قدرت تنه | قدرت ایستا | مهارت انگشتان | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی | حساسیت شنوایی | تشخیص رنگ بصری | انعطاف‌پذیری دامنه حرکت | جهت‌گیری پاسخ | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | سرعت کار تعیین‌شده توسط تجهیزات | تعیین وظایف، اولویت‌ها و اهداف | پیامد اشتباه | صرف زمان به صورت ایستاده | در معرض آلاینده‌ها | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فشار زمانی | اهمیت دقیق یا درست بودن کار | پیامدهای کاری و نتایج سایر کارکنان | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان به صورت پیاده‌روی یا دویدن | کار با یا مشارکت در یک گروه یا تیم کاری</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | سرعت تعیین‌شده توسط سرعت تجهیزات | تعیین وظایف، اولویت‌ها و اهداف | پیامد خطا | صرف زمان برای ایستادن | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فشار زمانی | اهمیت دقیق یا درست بودن | پیامدهای کاری و نتایج سایر کارکنان | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای راه رفتن یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیم</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌آلات اتصال چسبی | اپراتورها و متصدیان تجهیزات شستشو، پاکسازی و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات اکسترود، فرم‌دهی، پرس و متراکم‌سازی | اپراتورها و متصدیان کوره، تنور، خشک‌کن و دیگ‌های ذوب | کارگران سنگ‌زنی و پولیش دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرز و رنده فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات مخلوط‌کن و همزن | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | اپراتورها و متصدیان ماشین‌آلات بسته‌بندی و پرکنی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، fیلتراسیون، شفاف‌سازی، رسوب‌دهی و تقطیر | تیزکنندگان و ابزارسازان سنگ‌زنی و سوهان‌کاری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب، به جز اره‌کاری</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کننده | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Grinding and Polishing Workers, Hand</t>
+          <t>کارگران سنگ‌زنی و پرداخت دستی (Grinding and Polishing Workers, Hand)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | تفکر انتقادی | درک مطلب خوانده‌شده | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چالاکی انگشتان | دقت کنترل | بینایی نزدیک | چالاکی دست | هماهنگی چند عضو بدن | وضوح گفتار | تشخیص گفتار | توجه انتخابی | ترتیب‌دهی به اطلاعات | حساسیت به مسائل | درک شفاهی | انعطاف‌پذیری در بستن فضا | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | تجسم فضایی | سرعت ادراکی | تشخیص رنگ‌های بصری | قدرت بدنی بالاتنه | کنترل نرخ سرعت</t>
+          <t>ثبات دست و بازو | مهارت انگشتان | دقت کنترل | بینایی نزدیک | مهارت دستی | هماهنگی چند عضو | وضوح گفتار | تشخیص گفتار | توجه انتخابی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | درک شفاهی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | تجسم | سرعت ادراکی | تشخیص رنگ بصری | قدرت تنه | کنترل نرخ</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض تجهیزات خطرناک | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و در قالب تیم‌ها | در معرض آلاینده‌ها | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن کار | فشار زمانی | ارتباط با دیگران | صرف زمان به صورت ایستاده | صرف زمان برای انجام حرکات تکراری | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه یا تیم کاری | فضای بسته، با کنترل شرایط محیطی | اهمیت تکرار وظایف یکسان</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض تجهیزات خطرناک | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن | فشار زمانی | ارتباط با دیگران | صرف زمان برای ایستادن | صرف زمان برای انجام حرکات تکراری | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌آلات اتصال چسبی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردکن، سنگ‌شکن و پولیش | برش‌دهندگان و اصلاح‌کنندگان دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فورجینگ فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرز و رنده فلز و پلاستیک | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات اره‌کاری چوب | اپراتورها و متصدیان ماشین‌آلات کفش‌دوزی | تیزکنندگان و ابزارسازان سنگ‌زنی و سوهان‌کاری | قالب‌سازان و ابزارسازان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب، به جز اره‌کاری</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0091_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0091_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | مکانیک | زبان انگلیسی | شیمی | ریاضیات | مدیریت و امور اداری | آموزش و تدریس | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | حقوق و مقررات دولتی | مهندسی و فناوری | زیست‌شناسی | امور اداری و دفتری | تولید و فراوری</t>
+          <t>ایمنی و امنیت عمومی | مکانیک | زبان انگلیسی | شیمی | ریاضیات | مدیریت و اداره | آموزش و پرورش | خدمات مشتری و شخصی | رایانه و الکترونیک | قانون و دولت | مهندسی و فناوری | زیست‌شناسی | اداری | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | استدلال قیاسی | درک کتبی | دقت در کنترل ابزار | توجه انتخابی | مرتب‌سازی اطلاعات | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | قدرت عضلات بالاتنه | چابکی دستی | ثبات دست و بازو | سرعت ادراک | انعطاف‌پذیری ادراکی | وضوح گفتار | تشخیص گفتار | دید دور</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | استدلال قیاسی | درک کتبی | دقت کنترل | توجه انتخابی | ترتیب‌دهی اطلاعات | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | قدرت تنه | مهارت دستی | ثبات دست و بازو | سرعت ادراکی | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص گفتار | بینایی دور</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنسین‌های فراوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورهای تأسیسات و سیستم‌های شیمیایی | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و اسیدشویی فلزات | تکنسین‌های علوم زیست‌محیطی و بهداشت محیط | اپراتورهای ایستگاه‌های تقویت فشار و پمپاژ گاز | اپراتورهای تأسیسات و پالایشگاه‌های گاز | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های انرژی زمین‌گرمایی | کارگران پاکسازی و دفع مواد پرخطر | تکنسین‌های نیروگاه‌های برق‌آبی | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای نیروگاه برق | اپراتورهای پمپ به استثنای سرچاهی | کارگران بازیافت و بازیافت مواد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | سرویس‌کاران سپتیک‌تانک و لایروب‌های خطوط فاضلاب | مهندسان مکانیک تأسیسات و اپراتورهای بویلر | مهندسان آب و فاضلاب</t>
+          <t>تکنسین‌های فراوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | تکنسین‌های علوم و بهداشت محیط زیست | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | اپراتورهای تأسیسات و پالایشگاه‌های گاز | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های سامانه‌های زمین‌گرمایی | کارگران امحا و پاک‌سازی مواد خطرناک | تکنسین‌های نیروگاه برقابی | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | کارگران بازیافت و تفکیک پسماند | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال | یادگیری فعال | درک مطلب | سخن گفتن | نگارش</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | یادگیری فعال | درک مطلب | سخن گفتن | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>تولید و فراوری | شیمی | مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی</t>
+          <t>تولید و فرآوری | شیمی | مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | توجه انتخابی | دید نزدیک | بیان شفاهی | استدلال قیاسی | درک شفاهی | دید دور | دقت در کنترل ابزار | سرعت ادراک | مرتب‌سازی اطلاعات | حساسیت شنوایی | ثبات دست و بازو | درک کتبی | زمان واکنش | توجه شنیداری | وضوح گفتار | تشخیص گفتار | تشخیص تفکیکی رنگ‌ها | چابکی دستی | انعطاف‌پذیری ادراکی | استدلال استقرایی | بیان کتبی | چابکی انگشتان | انعطاف‌پذیری در طبقه‌بندی</t>
+          <t>حساسیت به مسئله | توجه انتخابی | بینایی نزدیک | بیان شفاهی | استدلال قیاسی | درک شفاهی | بینایی دور | دقت کنترل | سرعت ادراکی | ترتیب‌دهی اطلاعات | حساسیت شنوایی | ثبات دست و بازو | درک کتبی | زمان عکس‌العمل | توجه شنیداری | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | مهارت دستی | انعطاف‌پذیری بستار | استدلال استقرایی | بیان کتبی | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تکنسین‌های فراوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مهندسان شیمی | اپراتورها و متصدیان تجهیزات شیمیایی | تکنسین‌های شیمی | شیمیدان‌ها | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و اسیدشویی فلزات | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و دیگ‌های پخت | اپراتورهای ایستگاه‌های تقویت فشار و پمپاژ گاز | اپراتورهای تأسیسات و پالایشگاه‌های گاز | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلزات و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | اپراتورها و متصدیان کوره‌های ذوب و تصفیه فلزات | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای نیروگاه برق | اپراتورهای پمپ به استثنای سرچاهی | تکنسین‌های فراوری نیمه‌رساناها | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | مهندسان مکانیک تأسیسات و اپراتورهای بویلر | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
+          <t>تکنسین‌های فراوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مهندسان شیمی | اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | تکنسین‌های شیمی | شیمی‌دانان | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | اپراتورهای تأسیسات و پالایشگاه‌های گاز | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | تکنسین‌های فرآوری و ساخت نیمه‌هادی‌ها | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | درک مطلب | سخن گفتن | نگارش | شنیدن فعال</t>
+          <t>نظارت | تفکر انتقادی | درک مطلب | سخن گفتن | نگارش | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | مکانیک | زبان انگلیسی | رایانه و الکترونیک | ریاضیات | مهندسی و فناوری | تولید و فراوری | خدمات مشتریان و خدمات فردی | امور اداری و دفتری</t>
+          <t>ایمنی و امنیت عمومی | مکانیک | زبان انگلیسی | رایانه و الکترونیک | ریاضیات | مهندسی و فناوری | تولید و فرآوری | خدمات مشتری و شخصی | اداری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>سرعت ادراک | دید نزدیک | حساسیت به مسئله | توجه شنیداری | توجه انتخابی | درک شفاهی | استدلال قیاسی | انعطاف‌پذیری ادراکی | دید دور | زمان واکنش | مرتب‌سازی اطلاعات | بیان کتبی | درک کتبی | تسهیم توجه | تجسم فضایی | انعطاف‌پذیری در طبقه‌بندی | استدلال استقرایی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت شنوایی | تشخیص تفکیکی رنگ‌ها | کنترل نرخ حرکت | دقت در کنترل ابزار | چابکی انگشتان | چابکی دستی | ثبات دست و بازو</t>
+          <t>سرعت ادراکی | بینایی نزدیک | حساسیت به مسئله | توجه شنیداری | توجه انتخابی | درک شفاهی | استدلال قیاسی | انعطاف‌پذیری بستار | بینایی دور | زمان عکس‌العمل | ترتیب‌دهی اطلاعات | بیان کتبی | درک کتبی | تقسیم توجه | تجسم | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت شنوایی | تشخیص رنگ بصری | کنترل نرخ | دقت کنترل | مهارت انگشتان | مهارت دستی | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تکنسین‌های فراوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه زیست‌توده | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورهای تأسیسات و سیستم‌های شیمیایی | نصابان و تعمیرکاران شیرآلات و ادوات کنترلی به استثنای درب‌های اتوماتیک | اپراتورهای ایستگاه‌های تقویت فشار و پمپاژ گاز | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های انرژی زمین‌گرمایی | تکنسین‌های نیروگاه‌های برق‌آبی | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | توزیع‌کنندگان و دیسپچرهای شبکه برق | اپراتورهای نیروگاه برق | اپراتورهای پمپ به استثنای سرچاهی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | اپراتورهای خدمات چاه‌های نفت و گاز | مهندسان مکانیک تأسیسات و اپراتورهای بویلر | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | اپراتورهای پمپاژ سرچاهی | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
+          <t>تکنسین‌های فراوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های سامانه‌های زمین‌گرمایی | تکنسین‌های نیروگاه برقابی | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | دیسپچرها و توزیع‌کنندگان شبکه برق | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | اپراتورهای واحدهای خدمات چاه نفت و گاز | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | اپراتورهای پمپ سرچاهی نفت و گاز | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | درک مطلب | سخن گفتن | یادگیری فعال | تفکر انتقادی | نگارش | شنیدن فعال</t>
+          <t>نظارت | درک مطلب | سخن گفتن | یادگیری فعال | تفکر انتقادی | نگارش | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>تولید و فراوری | ایمنی و امنیت عمومی | مکانیک | مدیریت و امور اداری | ریاضیات | زبان انگلیسی</t>
+          <t>تولید و فرآوری | ایمنی و امنیت عمومی | مکانیک | مدیریت و اداره | ریاضیات | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>مرتب‌سازی اطلاعات | انعطاف‌پذیری ادراکی | سرعت ادراک | دید نزدیک | حساسیت به مسئله | توجه انتخابی | توجه شنیداری | حساسیت شنوایی | استدلال قیاسی | تشخیص گفتار | دقت در کنترل ابزار | انعطاف‌پذیری در طبقه‌بندی | استدلال استقرایی | بیان شفاهی | درک کتبی | درک شفاهی | چابکی انگشتان | چابکی دستی | ثبات دست و بازو | تجسم فضایی | بیان کتبی | تشخیص تفکیکی رنگ‌ها | دید دور | زمان واکنش | هماهنگی چند اندام | وضوح گفتار</t>
+          <t>ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | سرعت ادراکی | بینایی نزدیک | حساسیت به مسئله | توجه انتخابی | توجه شنیداری | حساسیت شنوایی | استدلال قیاسی | تشخیص گفتار | دقت کنترل | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | درک کتبی | درک شفاهی | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | تجسم | بیان کتبی | تشخیص رنگ بصری | بینایی دور | زمان عکس‌العمل | هماهنگی چند عضو | وضوح گفتار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنسین‌های فراوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه زیست‌توده | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورهای تأسیسات و سیستم‌های شیمیایی | نصابان و تعمیرکاران شیرآلات و ادوات کنترلی به استثنای درب‌های اتوماتیک | اپراتورهای ایستگاه‌های تقویت فشار و پمپاژ گاز | اپراتورهای تأسیسات و پالایشگاه‌های گاز | تکنسین‌های انرژی زمین‌گرمایی | تکنسین‌های نیروگاه‌های برق‌آبی | مهندسان نفت | توزیع‌کنندگان و دیسپچرهای شبکه برق | اپراتورهای نیروگاه برق | اپراتورهای پمپ به استثنای سرچاهی | حفاران دکل‌های دورانی چاه‌های نفت و گاز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | اپراتورهای خدمات چاه‌های نفت و گاز | مهندسان مکانیک تأسیسات و اپراتورهای بویلر | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | اپراتورهای پمپاژ سرچاهی</t>
+          <t>تکنسین‌های فراوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | اپراتورهای تأسیسات و پالایشگاه‌های گاز | تکنسین‌های سامانه‌های زمین‌گرمایی | تکنسین‌های نیروگاه برقابی | مهندسان نفت | دیسپچرها و توزیع‌کنندگان شبکه برق | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | حفاران دورانی نفت و گاز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | اپراتورهای واحدهای خدمات چاه نفت و گاز | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | اپراتورهای پمپ سرچاهی نفت و گاز</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مکانیک | تولید و فراوری | فیزیک | شیمی | رایانه و الکترونیک | زبان انگلیسی | ریاضیات | ایمنی و امنیت عمومی | مهندسی و فناوری</t>
+          <t>مکانیک | تولید و فرآوری | فیزیک | شیمی | رایانه و الکترونیک | زبان انگلیسی | ریاضیات | ایمنی و امنیت عمومی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | تجسم فضایی | ثبات دست و بازو | چابکی انگشتان | چابکی دستی | دقت در کنترل ابزار | هماهنگی چند اندام | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | استدلال ریاضی | دید دور | توجه شنیداری | زمان واکنش</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی دور | توجه شنیداری | زمان عکس‌العمل</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>اپراتورهای نیروگاه برق | مهندسان مکانیک تأسیسات و اپراتورهای بویلر | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | اپراتورهای تأسیسات و سیستم‌های شیمیایی | اپراتورهای تأسیسات و پالایشگاه‌های گاز | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای راکتورهای هسته‌ای | توزیع‌کنندگان و دیسپچرهای شبکه برق | تکنسین‌های نیروگاه زیست‌توده | تکنسین‌های نیروگاه‌های برق‌آبی | تکنسین‌های فراوری سوخت‌های زیستی | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورهای ایستگاه‌های تقویت فشار و پمپاژ گاز | اپراتورهای پمپ به استثنای سرچاهی | مکانیک‌های ماشین‌آلات صنعتی | کارگران عمومی تعمیر و نگهداری | سرپرستان رده‌اول کارگران تولید و عملیات | نصابان و تعمیرکاران شیرآلات و ادوات کنترلی به استثنای درب‌های اتوماتیک | تکنسین‌های ایمنی و بهداشت حرفه‌ای | سایر کارگران حوزه تولید</t>
+          <t>اپراتورهای نیروگاه برق | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | اپراتورهای تأسیسات و پالایشگاه‌های گاز | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای رآکتور نیروگاه هسته‌ای | دیسپچرها و توزیع‌کنندگان شبکه برق | تکنسین‌های نیروگاه زیست‌توده | تکنسین‌های نیروگاه برقابی | تکنسین‌های فراوری سوخت‌های زیستی | اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | مکانیک‌های ماشین‌آلات صنعتی | کارگران عمومی تعمیرات و نگهداری تاسیسات | سرپرستان رده اول کارگران تولید و عملیات | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | کاردان‌ها و تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | سایر کارگران خطوط تولید</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | سخن گفتن | شنیدن فعال | نگارش | تفکر انتقادی</t>
+          <t>درک مطلب | نظارت | سخن گفتن | گوش دادن فعال | نگارش | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>تولید و فراوری | مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | شیمی | رایانه و الکترونیک</t>
+          <t>تولید و فرآوری | مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | شیمی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دقت در کنترل ابزار | تشخیص گفتار | درک شفاهی | بیان شفاهی | درک کتبی | ثبات دست و بازو | توجه انتخابی | سرعت ادراک | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | زمان واکنش | چابکی دستی | وضوح گفتار | تشخیص تفکیکی رنگ‌ها | دید نزدیک | چابکی انگشتان | هماهنگی چند اندام | بیان کتبی | توجه شنیداری | کنترل نرخ حرکت | تسهیم توجه | انعطاف‌پذیری ادراکی | انعطاف‌پذیری در طبقه‌بندی | تجسم فضایی | دید دور | انعطاف‌پذیری گسترده بدن | قدرت عضلات بالاتنه | حساسیت شنوایی</t>
+          <t>دقت کنترل | تشخیص گفتار | درک شفاهی | بیان شفاهی | درک کتبی | ثبات دست و بازو | توجه انتخابی | سرعت ادراکی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | زمان عکس‌العمل | مهارت دستی | وضوح گفتار | تشخیص رنگ بصری | بینایی نزدیک | مهارت انگشتان | هماهنگی چند عضو | بیان کتبی | توجه شنیداری | کنترل نرخ | تقسیم توجه | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | تجسم | بینایی دور | انعطاف‌پذیری دامنه حرکت | قدرت تنه | حساسیت شنوایی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنسین‌های کشاورزی | مدیران تولید سوخت‌های زیستی | مدیران توسعه فناوری و محصولات بیودیزل و سوخت زیستی | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه زیست‌توده | مهندسان شیمی | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورهای تأسیسات و سیستم‌های شیمیایی | اپراتورهای ایستگاه‌های تقویت فشار و پمپاژ گاز | اپراتورهای تأسیسات و پالایشگاه‌های گاز | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های انرژی زمین‌گرمایی | تکنسین‌های نیروگاه‌های برق‌آبی | تکنسین‌ها و کاردان‌های مهندسی صنایع | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای نیروگاه برق | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | مهندسان مکانیک تأسیسات و اپراتورهای بویلر | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | اپراتورهای پمپاژ سرچاهی</t>
+          <t>تکنسین‌های کشاورزی | مدیران تولید سوخت‌های زیستی | مدیران توسعه محصول و فناوری زیست‌سوخت | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مهندسان شیمی | اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | اپراتورهای تأسیسات و پالایشگاه‌های گاز | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های سامانه‌های زمین‌گرمایی | تکنسین‌های نیروگاه برقابی | کارشناسان و تکنسین‌های مهندسی صنایع | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای نیروگاه برق | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | اپراتورهای پمپ سرچاهی نفت و گاز</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | یادگیری فعال | نگارش</t>
+          <t>نظارت | درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>تولید و فراوری | شیمی | مکانیک | رایانه و الکترونیک | زبان انگلیسی | ریاضیات | ایمنی و امنیت عمومی | حقوق و مقررات دولتی | امور اداری و دفتری | مدیریت و امور اداری | مهندسی و فناوری | آموزش و تدریس</t>
+          <t>تولید و فرآوری | شیمی | مکانیک | رایانه و الکترونیک | زبان انگلیسی | ریاضیات | ایمنی و امنیت عمومی | قانون و دولت | اداری | مدیریت و اداره | مهندسی و فناوری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | دقت در کنترل ابزار | دید نزدیک | درک کتبی | سرعت ادراک | دید دور | هماهنگی چند اندام | مرتب‌سازی اطلاعات | چابکی دستی | زمان واکنش | بیان کتبی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | کنترل نرخ حرکت | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری ادراکی | استدلال استقرایی | توجه شنیداری | تشخیص تفکیکی رنگ‌ها | چابکی انگشتان | تجسم فضایی | انعطاف‌پذیری در طبقه‌بندی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | دقت کنترل | بینایی نزدیک | درک کتبی | سرعت ادراکی | بینایی دور | هماهنگی چند عضو | ترتیب‌دهی اطلاعات | مهارت دستی | زمان عکس‌العمل | بیان کتبی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | کنترل نرخ | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری بستار | استدلال استقرایی | توجه شنیداری | تشخیص رنگ بصری | مهارت انگشتان | تجسم | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنسین‌های فراوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مهندسان شیمی | اپراتورهای تأسیسات و سیستم‌های شیمیایی | تکنسین‌های شیمی | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌شکنی، آسیاب و پرداخت | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و دیگ‌های پخت | اپراتورهای ایستگاه‌های تقویت فشار و پمپاژ گاز | اپراتورهای تأسیسات و پالایشگاه‌های گاز | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلزات و پلاستیک | اپراتورها و متصدیان کوره‌های ذوب و تصفیه فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات اختلاط و ترکیب مواد | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات آبکاری فلزات و پلاستیک | اپراتورهای نیروگاه برق | اپراتورهای پمپ به استثنای سرچاهی | تکنسین‌های فراوری نیمه‌رساناها | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
+          <t>تکنسین‌های فراوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مهندسان شیمی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | تکنسین‌های شیمی | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | اپراتورهای تأسیسات و پالایشگاه‌های گاز | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | تنظیم‌کاران و اپراتورهای دستگاه‌های آبکاری فلز و پلاستیک | اپراتورهای نیروگاه برق | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | تکنسین‌های فرآوری و ساخت نیمه‌هادی‌ها | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | شنیدن فعال | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و فراوری | مکانیک | زبان انگلیسی</t>
+          <t>تولید و فرآوری | مکانیک | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | سرعت ادراک | حساسیت به مسئله | ثبات دست و بازو | مرتب‌سازی اطلاعات | زمان واکنش | قدرت ایستایی عضلانی | هماهنگی چند اندام | دقت در کنترل ابزار | توجه انتخابی | انعطاف‌پذیری ادراکی | درک شفاهی | انعطاف‌پذیری در طبقه‌بندی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | تشخیص گفتار | حساسیت شنوایی | تشخیص تفکیکی رنگ‌ها | دید دور | تعادل بدنی | انعطاف‌پذیری گسترده بدن | قدرت عضلات بالاتنه | کنترل نرخ حرکت | چابکی انگشتان | چابکی دستی | تجسم فضایی</t>
+          <t>بینایی نزدیک | سرعت ادراکی | حساسیت به مسئله | ثبات دست و بازو | ترتیب‌دهی اطلاعات | زمان عکس‌العمل | قدرت ایستا | هماهنگی چند عضو | دقت کنترل | توجه انتخابی | انعطاف‌پذیری بستار | درک شفاهی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | تشخیص گفتار | حساسیت شنوایی | تشخیص رنگ بصری | بینایی دور | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | قدرت تنه | کنترل نرخ | مهارت انگشتان | مهارت دستی | تجسم</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌های نیروگاه زیست‌توده | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورهای تأسیسات و سیستم‌های شیمیایی | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و اسیدشویی فلزات | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌شکنی، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان اکستروژن و فرم‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات اکستروژن، فرم‌دهی، پرس و فشرده‌سازی | فرمول‌سازان و پیمانه‌کاران صنایع غذایی | اپراتورها و متصدیان ماشین‌آلات پخت مواد غذایی | اپراتورها و متصدیان ماشین‌آلات برشته‌کاری، پخت و خشک‌کن صنایع غذایی و دخانیات | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و دیگ‌های پخت | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلزات و پلاستیک | کارگران تغذیه و تخلیه ماشین‌آلات | اپراتورها و متصدیان کوره‌های ذوب و تصفیه فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات اختلاط و ترکیب مواد | اپراتورها و متصدیان ماشین‌آلات بسته‌بندی و پرکن | اپراتورهای پمپ به استثنای سرچاهی | اپراتورها و متصدیان ماشین‌آلات رنگرزی و سفیدگری منسوجات | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
+          <t>تکنسین‌های نیروگاه زیست‌توده | اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌آلات پخت مواد غذایی | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,22 +959,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>نرم‌افزار SAP | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار Microsoft Office</t>
+          <t>نرم‌افزار ایمیل | Microsoft Excel | نرم‌افزار Microsoft Office | نرم‌افزار ایمیل | نرم‌افزار SAP</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | تولید و فراوری | زبان انگلیسی | آموزش و تدریس | ایمنی و امنیت عمومی</t>
+          <t>مدیریت و اداره | تولید و فرآوری | زبان انگلیسی | آموزش و پرورش | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>چابکی دستی | دقت در کنترل ابزار | زمان واکنش | کنترل نرخ حرکت | هماهنگی چند اندام | ثبات دست و بازو | دید نزدیک | حساسیت به مسئله | توجه شنیداری | قدرت عضلات بالاتنه | قدرت ایستایی عضلانی | چابکی انگشتان | سرعت ادراک | انعطاف‌پذیری ادراکی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی | حساسیت شنوایی | تشخیص تفکیکی رنگ‌ها | انعطاف‌پذیری گسترده بدن | جهت‌یابی پاسخ | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری در طبقه‌بندی | وضوح گفتار | تشخیص گفتار</t>
+          <t>مهارت دستی | دقت کنترل | زمان عکس‌العمل | کنترل نرخ | هماهنگی چند عضو | ثبات دست و بازو | بینایی نزدیک | حساسیت به مسئله | توجه شنیداری | قدرت تنه | قدرت ایستا | مهارت انگشتان | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی | حساسیت شنوایی | تشخیص رنگ بصری | انعطاف‌پذیری دامنه حرکت | جهت‌گیری پاسخ | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌آلات چسب‌زنی و اتصال | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش، پانچ و پرس فلزات و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات اکستروژن، فرم‌دهی، پرس و فشرده‌سازی | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و دیگ‌های پخت | پرداخت‌کاران و سنگ‌زنان دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و بافینگ فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تراشکاری فلزات و پلاستیک | کارگران تغذیه و تخلیه ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های فرزکاری و صفحه‌تراشی فلزات و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات اختلاط و ترکیب مواد | قالب‌گیران، فرم‌دهندگان و ریخته‌گران به استثنای فلزات و پلاستیک | اپراتورها و متصدیان ماشین‌آلات بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات نورد فلزات و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات نجاری و صنایع چوب به استثنای اره‌کاری</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>تولید و فراوری | مکانیک | زبان انگلیسی</t>
+          <t>تولید و فرآوری | مکانیک | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی انگشتان | دقت در کنترل ابزار | دید نزدیک | چابکی دستی | هماهنگی چند اندام | وضوح گفتار | تشخیص گفتار | توجه انتخابی | مرتب‌سازی اطلاعات | حساسیت به مسئله | درک شفاهی | انعطاف‌پذیری ادراکی | انعطاف‌پذیری در طبقه‌بندی | بیان شفاهی | تجسم فضایی | سرعت ادراک | تشخیص تفکیکی رنگ‌ها | قدرت عضلات بالاتنه | کنترل نرخ حرکت</t>
+          <t>ثبات دست و بازو | مهارت انگشتان | دقت کنترل | بینایی نزدیک | مهارت دستی | هماهنگی چند عضو | وضوح گفتار | تشخیص گفتار | توجه انتخابی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | درک شفاهی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | تجسم | سرعت ادراکی | تشخیص رنگ بصری | قدرت تنه | کنترل نرخ</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌آلات چسب‌زنی و اتصال | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | برشکاران و پیرایندگان دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش، پانچ و پرس فلزات و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات آهنگری و فورج فلزات و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و بافینگ فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تراشکاری فلزات و پلاستیک | کارگران تغذیه و تخلیه ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های فرزکاری و صفحه‌تراشی فلزات و پلاستیک | قالب‌گیران، فرم‌دهندگان و ریخته‌گران به استثنای فلزات و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای چندکاره فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات نورد فلزات و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان اره‌کشی چوب | اپراتورها و متصدیان ماشین‌آلات کفاشی | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات نجاری و صنایع چوب به استثنای اره‌کاری</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | اپراتورها و متصدیان ماشین‌آلات کفش | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
